--- a/data/raw/时间序列数据.xlsx
+++ b/data/raw/时间序列数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuanhm\Documents\GitHub\bse_dashboard\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411E47BC-F01C-4BC6-A452-CB986939F502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F176C1DE-A898-4A24-8F1D-6B1809B37146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17539,15 +17539,15 @@
       </c>
       <c r="B1006" s="1">
         <f>[1]!s_dq_close("399006.SZ",A1006,3)</f>
-        <v>4192.1944999999996</v>
+        <v>4251.4243999999999</v>
       </c>
       <c r="C1006" s="1">
         <f>[1]!s_dq_close("000688.SH",A1006,3)</f>
-        <v>1916.2122999999999</v>
+        <v>1989.4257</v>
       </c>
       <c r="D1006" s="2">
         <f>[1]!s_dq_close("899050",A1006,3)</f>
-        <v>1281.2127</v>
+        <v>1295.9537</v>
       </c>
     </row>
   </sheetData>
